--- a/data/trans_orig/IP18-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP18-Estudios-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4884</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13851</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11005</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,12 +1707,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9725</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21290</t>
+          <t>21594</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53972</t>
+          <t>54709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64369</t>
+          <t>64160</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58906</t>
+          <t>58566</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68494</t>
+          <t>68163</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>116623</t>
+          <t>116362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130173</t>
+          <t>130126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,46%</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2319,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>13516</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17409</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>12452</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25865</t>
+          <t>26414</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -2545,12 +2545,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>10858</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -2658,12 +2658,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>772</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>11748</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -2771,12 +2771,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>16433</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>14671</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13664</t>
+          <t>13696</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28136</t>
+          <t>27592</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -2884,12 +2884,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33271</t>
+          <t>32616</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>53285</t>
+          <t>52598</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2899,12 +2899,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35755</t>
+          <t>35311</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>54767</t>
+          <t>55146</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>73096</t>
+          <t>73443</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>102579</t>
+          <t>102885</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -2997,12 +2997,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>288738</t>
+          <t>289860</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>314134</t>
+          <t>312391</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>320898</t>
+          <t>321573</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>347470</t>
+          <t>346283</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>616602</t>
+          <t>616308</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>651709</t>
+          <t>652909</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,52%</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8559</t>
+          <t>8582</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13824</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -3679,12 +3679,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13784</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14306</t>
+          <t>14319</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11383</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24023</t>
+          <t>23661</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -3792,12 +3792,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13729</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7777</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -4131,12 +4131,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11389</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>23946</t>
+          <t>23698</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4146,12 +4146,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>10265</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21952</t>
+          <t>22259</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>23829</t>
+          <t>23533</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>42082</t>
+          <t>41989</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>107666</t>
+          <t>107844</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>125378</t>
+          <t>125736</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>90564</t>
+          <t>91350</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>107547</t>
+          <t>107995</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>203791</t>
+          <t>205279</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>228790</t>
+          <t>230491</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,67%</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -4813,12 +4813,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t>14023</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>23648</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -4926,12 +4926,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>10374</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>24037</t>
+          <t>23982</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>13375</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>26900</t>
+          <t>27354</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>27952</t>
+          <t>27686</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>47525</t>
+          <t>47134</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>13750</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>22859</t>
+          <t>22486</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>7707</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>13891</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>18130</t>
+          <t>19086</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -5265,12 +5265,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>17295</t>
+          <t>17146</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>8697</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>20351</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>17212</t>
+          <t>17477</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>33866</t>
+          <t>33945</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>55510</t>
+          <t>56499</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>81599</t>
+          <t>80469</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>55326</t>
+          <t>55828</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>79532</t>
+          <t>79334</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>117176</t>
+          <t>115289</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>153970</t>
+          <t>150867</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>461914</t>
+          <t>462402</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>493226</t>
+          <t>493834</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>482173</t>
+          <t>481446</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>514628</t>
+          <t>512895</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>954839</t>
+          <t>954680</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>998578</t>
+          <t>998159</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -6517,12 +6517,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>679</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>865</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -6630,12 +6630,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9752</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>452</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -6856,12 +6856,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9837</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6871,82 +6871,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3326</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1244</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8207</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>10,39%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>8662</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>4798</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>13936</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>2,88%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,19%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3326</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1266</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7044</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>8662</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>5236</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>14928</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -6969,12 +6969,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71088</t>
+          <t>70896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81280</t>
+          <t>81323</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64276</t>
+          <t>64077</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73877</t>
+          <t>73941</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7019,12 +7019,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139173</t>
+          <t>139469</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>152879</t>
+          <t>153091</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7054,12 +7054,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>480</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>480</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -7538,12 +7538,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7553,49 +7553,49 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4810</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>10733</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
           <t>2,27%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>4810</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1771</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>9960</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>13</t>
@@ -7608,12 +7608,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16113</t>
+          <t>16318</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -7651,12 +7651,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13508</t>
+          <t>13527</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16525</t>
+          <t>17114</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7701,12 +7701,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12249</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26775</t>
+          <t>25470</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -7764,12 +7764,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>16518</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>11405</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7814,12 +7814,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>11251</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24394</t>
+          <t>24578</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -7877,12 +7877,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11858</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7187</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18425</t>
+          <t>18187</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7927,12 +7927,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25928</t>
+          <t>26016</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7962,12 +7962,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -7990,12 +7990,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>14373</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11402</t>
+          <t>11768</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25199</t>
+          <t>24812</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18721</t>
+          <t>18492</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35412</t>
+          <t>34962</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -8103,12 +8103,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22452</t>
+          <t>21479</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>37872</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21601</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38985</t>
+          <t>38784</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47795</t>
+          <t>47979</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>71261</t>
+          <t>70826</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -8216,12 +8216,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>345960</t>
+          <t>345757</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>370179</t>
+          <t>371252</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8251,12 +8251,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>378296</t>
+          <t>378946</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>404979</t>
+          <t>406009</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>733614</t>
+          <t>733998</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>769369</t>
+          <t>770903</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -8677,7 +8677,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -8785,12 +8785,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12992</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22528</t>
+          <t>21628</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -8898,12 +8898,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14524</t>
+          <t>13991</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -9011,12 +9011,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9061,12 +9061,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>13069</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12050</t>
+          <t>12710</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>14675</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9209,12 +9209,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -9237,12 +9237,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -9272,12 +9272,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -9287,12 +9287,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -9307,12 +9307,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>15254</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -9322,12 +9322,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -9350,12 +9350,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16991</t>
+          <t>17502</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9385,12 +9385,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14050</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9420,12 +9420,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>27365</t>
+          <t>26993</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9435,12 +9435,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -9463,12 +9463,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>115514</t>
+          <t>114302</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>131498</t>
+          <t>132181</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>119272</t>
+          <t>118824</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>136501</t>
+          <t>136353</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9513,12 +9513,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9533,12 +9533,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>239575</t>
+          <t>238296</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>263306</t>
+          <t>263815</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9548,12 +9548,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,07%</t>
         </is>
       </c>
     </row>
@@ -9693,12 +9693,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>477</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9989,12 +9989,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -10032,12 +10032,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>20140</t>
+          <t>19194</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6652</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>18549</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10082,12 +10082,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10102,12 +10102,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>17190</t>
+          <t>17602</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>32919</t>
+          <t>32980</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>8003</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>20663</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>22071</t>
+          <t>21145</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10195,12 +10195,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>20071</t>
+          <t>19737</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>37908</t>
+          <t>37753</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10230,12 +10230,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -10258,12 +10258,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>22629</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10273,12 +10273,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10293,12 +10293,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>17981</t>
+          <t>18456</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10308,12 +10308,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10328,12 +10328,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>19052</t>
+          <t>19073</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>37185</t>
+          <t>35995</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -10371,12 +10371,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>16341</t>
+          <t>17053</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10386,12 +10386,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>14976</t>
+          <t>14685</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>30086</t>
+          <t>29398</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10421,12 +10421,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>23449</t>
+          <t>22954</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>42480</t>
+          <t>41396</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10456,12 +10456,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -10484,12 +10484,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>20316</t>
+          <t>21582</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10499,12 +10499,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>17160</t>
+          <t>16072</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>32116</t>
+          <t>32173</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10534,12 +10534,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>28607</t>
+          <t>28618</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>48717</t>
+          <t>48045</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -10597,12 +10597,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>35843</t>
+          <t>35114</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>56662</t>
+          <t>56089</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10612,12 +10612,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>32256</t>
+          <t>31694</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>52419</t>
+          <t>52764</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10647,47 +10647,47 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>86046</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>72862</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>101689</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
           <t>7,31%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>86046</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>71785</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>100594</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>542229</t>
+          <t>543805</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>573482</t>
+          <t>575771</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10725,12 +10725,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10745,12 +10745,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>573058</t>
+          <t>573221</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>606782</t>
+          <t>608055</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1129864</t>
+          <t>1126742</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1175655</t>
+          <t>1172735</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,35%</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -11849,12 +11849,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11864,12 +11864,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4244</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11919,12 +11919,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -11962,12 +11962,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>584</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12032,12 +12032,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7626</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -12075,12 +12075,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>630</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12090,12 +12090,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12145,12 +12145,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7937</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12160,12 +12160,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -12188,12 +12188,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40974</t>
+          <t>41299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50173</t>
+          <t>50259</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12203,12 +12203,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12223,12 +12223,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54843</t>
+          <t>54824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61568</t>
+          <t>61689</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12258,12 +12258,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99372</t>
+          <t>98717</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110524</t>
+          <t>110430</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12273,12 +12273,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,94%</t>
         </is>
       </c>
     </row>
@@ -12757,12 +12757,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12772,12 +12772,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>15029</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12807,12 +12807,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12827,12 +12827,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12325</t>
+          <t>12833</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26170</t>
+          <t>26513</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -12870,12 +12870,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12940,12 +12940,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>14158</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -12983,12 +12983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>13684</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13053,12 +13053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>20680</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13068,12 +13068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -13096,12 +13096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>9492</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9773</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13166,12 +13166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14631</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -13209,12 +13209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17095</t>
+          <t>17203</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16728</t>
+          <t>17070</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13279,12 +13279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14678</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>29628</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13294,12 +13294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -13322,12 +13322,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18220</t>
+          <t>18778</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12521</t>
+          <t>12768</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26114</t>
+          <t>26353</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13392,12 +13392,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22784</t>
+          <t>22936</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>39555</t>
+          <t>39592</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -13435,12 +13435,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>376436</t>
+          <t>376841</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>398483</t>
+          <t>397701</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13450,12 +13450,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>376403</t>
+          <t>375982</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>398475</t>
+          <t>397675</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13505,12 +13505,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>761159</t>
+          <t>761548</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>791528</t>
+          <t>791749</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13520,12 +13520,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,26%</t>
         </is>
       </c>
     </row>
@@ -13818,7 +13818,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13833,7 +13833,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13853,7 +13853,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -14004,12 +14004,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14701</t>
+          <t>15479</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14019,12 +14019,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14039,12 +14039,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18399</t>
+          <t>18235</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14054,12 +14054,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14074,12 +14074,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15174</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29408</t>
+          <t>28921</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14089,12 +14089,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -14117,12 +14117,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>9361</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14152,12 +14152,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11265</t>
+          <t>11717</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14187,12 +14187,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>17345</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14202,12 +14202,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -14230,12 +14230,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>496</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14245,12 +14245,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14265,12 +14265,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14300,12 +14300,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14315,12 +14315,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -14348,7 +14348,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14378,12 +14378,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14413,12 +14413,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14428,12 +14428,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14476,7 +14476,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -14491,12 +14491,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -14506,12 +14506,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>9696</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -14541,12 +14541,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -14569,12 +14569,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11849</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14584,12 +14584,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14604,12 +14604,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14619,12 +14619,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14639,12 +14639,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>16906</t>
+          <t>16350</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14654,12 +14654,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -14682,12 +14682,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>122663</t>
+          <t>122528</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>137057</t>
+          <t>136818</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14717,12 +14717,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>132013</t>
+          <t>132558</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>148802</t>
+          <t>149355</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14752,12 +14752,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>260181</t>
+          <t>261158</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>281393</t>
+          <t>282888</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14767,12 +14767,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,34%</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -15251,12 +15251,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12810</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26733</t>
+          <t>26773</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15286,12 +15286,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>15224</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>29856</t>
+          <t>30602</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>32922</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>54384</t>
+          <t>52675</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15336,12 +15336,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -15364,12 +15364,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>16830</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15384,7 +15384,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15399,12 +15399,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>16392</t>
+          <t>16086</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15434,12 +15434,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>28613</t>
+          <t>28974</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15449,12 +15449,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -15477,12 +15477,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15492,12 +15492,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15512,12 +15512,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>13541</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15532,7 +15532,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15547,12 +15547,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>12521</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>26511</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15562,12 +15562,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -15590,12 +15590,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15605,12 +15605,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15625,12 +15625,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>13009</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15640,12 +15640,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15660,12 +15660,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>23058</t>
+          <t>23248</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -15703,12 +15703,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>9419</t>
+          <t>9429</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>21066</t>
+          <t>21593</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15738,12 +15738,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>22531</t>
+          <t>22173</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15753,12 +15753,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15773,12 +15773,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>21699</t>
+          <t>21086</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>40165</t>
+          <t>38796</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15788,12 +15788,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -15816,12 +15816,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>14331</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>29366</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -15831,12 +15831,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -15851,12 +15851,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>16817</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>32052</t>
+          <t>32226</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -15866,12 +15866,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -15886,12 +15886,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>35128</t>
+          <t>33576</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>56669</t>
+          <t>56084</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -15901,12 +15901,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -15929,12 +15929,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>550944</t>
+          <t>551763</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>577832</t>
+          <t>578418</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -15944,12 +15944,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -15964,12 +15964,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>572629</t>
+          <t>573694</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>602154</t>
+          <t>601643</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -15999,12 +15999,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1133084</t>
+          <t>1134394</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1171812</t>
+          <t>1172725</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,59%</t>
         </is>
       </c>
     </row>
@@ -16395,7 +16395,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -16960,7 +16960,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -16975,7 +16975,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -17030,7 +17030,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -17073,7 +17073,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -17108,7 +17108,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -17158,7 +17158,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -17256,7 +17256,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -17271,7 +17271,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -17299,7 +17299,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -17334,7 +17334,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -17349,7 +17349,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -17369,7 +17369,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -17384,7 +17384,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -17422,12 +17422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -17442,7 +17442,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -17457,7 +17457,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -17477,12 +17477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14012</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -17492,12 +17492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,24%</t>
         </is>
       </c>
     </row>
@@ -17755,7 +17755,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -17770,7 +17770,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -17820,12 +17820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>892</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>9880</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -17835,12 +17835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -17981,7 +17981,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -18031,7 +18031,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -18046,12 +18046,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -18061,12 +18061,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -18089,12 +18089,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17786</t>
+          <t>16229</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -18104,12 +18104,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -18129,7 +18129,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -18159,12 +18159,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19392</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -18174,12 +18174,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -18202,12 +18202,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>9396</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -18217,12 +18217,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -18237,12 +18237,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>778</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>6569</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -18252,12 +18252,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -18272,12 +18272,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -18287,12 +18287,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -18320,7 +18320,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -18335,7 +18335,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -18350,12 +18350,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>9694</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -18365,12 +18365,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -18385,12 +18385,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -18400,12 +18400,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -18428,12 +18428,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -18443,12 +18443,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -18463,12 +18463,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -18478,12 +18478,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -18498,12 +18498,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>23260</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -18513,12 +18513,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -18541,12 +18541,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>808</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -18556,12 +18556,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -18576,12 +18576,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>769</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -18591,12 +18591,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -18611,12 +18611,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -18626,12 +18626,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -18654,12 +18654,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34414</t>
+          <t>34216</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48686</t>
+          <t>49276</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -18669,12 +18669,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -18689,12 +18689,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61240</t>
+          <t>60307</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>76573</t>
+          <t>76951</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -18704,12 +18704,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -18724,12 +18724,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>98940</t>
+          <t>99083</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>121858</t>
+          <t>121252</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -18739,12 +18739,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>76,99%</t>
         </is>
       </c>
     </row>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -19017,7 +19017,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -19052,7 +19052,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -19067,12 +19067,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>546</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -19082,12 +19082,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -19223,12 +19223,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>486</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -19238,12 +19238,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -19293,12 +19293,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>459</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -19308,12 +19308,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -19341,7 +19341,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -19356,7 +19356,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -19371,12 +19371,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>575</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -19386,12 +19386,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -19406,12 +19406,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -19421,12 +19421,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -19449,12 +19449,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -19464,12 +19464,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -19489,7 +19489,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -19519,12 +19519,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -19534,12 +19534,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -19567,7 +19567,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -19582,7 +19582,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -19597,12 +19597,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>480</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -19612,12 +19612,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -19632,12 +19632,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -19647,12 +19647,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -19690,12 +19690,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -19710,12 +19710,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -19725,12 +19725,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -19745,12 +19745,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>11662</t>
+          <t>11612</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -19760,12 +19760,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -19828,7 +19828,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -19843,7 +19843,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -19878,7 +19878,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -19901,12 +19901,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>13355</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -19916,12 +19916,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -19936,12 +19936,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>15161</t>
+          <t>15216</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>24352</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -19951,12 +19951,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -19971,12 +19971,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>30928</t>
+          <t>31473</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>43255</t>
+          <t>43416</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -19986,12 +19986,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,29%</t>
         </is>
       </c>
     </row>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -20151,7 +20151,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -20206,7 +20206,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -20221,7 +20221,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -20244,12 +20244,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -20279,12 +20279,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>8785</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -20294,12 +20294,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -20314,12 +20314,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -20329,12 +20329,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -20470,12 +20470,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -20485,12 +20485,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -20510,7 +20510,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -20540,12 +20540,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -20555,12 +20555,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -20583,12 +20583,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -20598,12 +20598,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -20618,12 +20618,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -20633,12 +20633,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -20653,12 +20653,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>22649</t>
+          <t>23412</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -20668,12 +20668,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -20696,12 +20696,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -20711,12 +20711,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -20731,12 +20731,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -20746,12 +20746,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -20766,12 +20766,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>17987</t>
+          <t>18367</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -20781,12 +20781,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -20809,12 +20809,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -20824,12 +20824,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>15007</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -20859,12 +20859,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -20879,12 +20879,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>17234</t>
+          <t>17431</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -20894,12 +20894,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -20922,12 +20922,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>15406</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -20937,12 +20937,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -20957,12 +20957,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>20861</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -20972,12 +20972,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -20992,12 +20992,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>13694</t>
+          <t>13361</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>30650</t>
+          <t>30777</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -21007,12 +21007,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -21035,12 +21035,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -21050,12 +21050,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -21070,12 +21070,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -21085,12 +21085,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -21105,12 +21105,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>14434</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -21120,12 +21120,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -21148,12 +21148,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>53354</t>
+          <t>53250</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>70778</t>
+          <t>71102</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -21163,12 +21163,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -21183,12 +21183,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>86907</t>
+          <t>86502</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>107189</t>
+          <t>105910</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -21198,12 +21198,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -21218,12 +21218,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>146680</t>
+          <t>145173</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>172286</t>
+          <t>172755</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -21233,12 +21233,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,49%</t>
         </is>
       </c>
     </row>
